--- a/Testing Data/Study Plan/WUAFM.xlsx
+++ b/Testing Data/Study Plan/WUAFM.xlsx
@@ -1,28 +1,202 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\HKIT Course Management System V2\Testing Data\Study Plan\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD450DC6-4E26-4A36-A765-7CB4E82223B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="56">
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>Intake Level</t>
+  </si>
+  <si>
+    <t>student ID</t>
+  </si>
+  <si>
+    <t>Intake term</t>
+  </si>
+  <si>
+    <t>study mode</t>
+  </si>
+  <si>
+    <t>programme stream</t>
+  </si>
+  <si>
+    <t>Module code</t>
+  </si>
+  <si>
+    <t>Study term</t>
+  </si>
+  <si>
+    <t>Lee Kam Shuen</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>22655001</t>
+  </si>
+  <si>
+    <t>T2026A</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>nil</t>
+  </si>
+  <si>
+    <t>BS406</t>
+  </si>
+  <si>
+    <t>HD403</t>
+  </si>
+  <si>
+    <t>HD407</t>
+  </si>
+  <si>
+    <t>HD405</t>
+  </si>
+  <si>
+    <t>GS402</t>
+  </si>
+  <si>
+    <t>BS401</t>
+  </si>
+  <si>
+    <t>T2026B</t>
+  </si>
+  <si>
+    <t>BS402</t>
+  </si>
+  <si>
+    <t>BS408</t>
+  </si>
+  <si>
+    <t>HD404</t>
+  </si>
+  <si>
+    <t>HD406</t>
+  </si>
+  <si>
+    <t>AF401</t>
+  </si>
+  <si>
+    <t>AF402</t>
+  </si>
+  <si>
+    <t>BUS692</t>
+  </si>
+  <si>
+    <t>T2026C</t>
+  </si>
+  <si>
+    <t>BUS688</t>
+  </si>
+  <si>
+    <t>BUS699</t>
+  </si>
+  <si>
+    <t>T2027A</t>
+  </si>
+  <si>
+    <t>BUS694</t>
+  </si>
+  <si>
+    <t>BUS689</t>
+  </si>
+  <si>
+    <t>Choi Siu Yan</t>
+  </si>
+  <si>
+    <t>22655002</t>
+  </si>
+  <si>
+    <t>Tong Ka Ki</t>
+  </si>
+  <si>
+    <t>22655003</t>
+  </si>
+  <si>
+    <t>BS414</t>
+  </si>
+  <si>
+    <t>Hung Hiu Ting</t>
+  </si>
+  <si>
+    <t>22655004</t>
+  </si>
+  <si>
+    <t>Leung Cho Tung</t>
+  </si>
+  <si>
+    <t>22655005</t>
+  </si>
+  <si>
+    <t>Lau Kin Shun</t>
+  </si>
+  <si>
+    <t>22655006</t>
+  </si>
+  <si>
+    <t>BS410</t>
+  </si>
+  <si>
+    <t>Leung Cho Yung</t>
+  </si>
+  <si>
+    <t>22655007</t>
+  </si>
+  <si>
+    <t>Chan Sze Wing</t>
+  </si>
+  <si>
+    <t>22655008</t>
+  </si>
+  <si>
+    <t>Lee Fuk Chuen</t>
+  </si>
+  <si>
+    <t>32655001</t>
+  </si>
+  <si>
+    <t>Shi Federickson Chau</t>
+  </si>
+  <si>
+    <t>32655002</t>
+  </si>
+  <si>
+    <t>BS407</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,7 +230,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -79,44 +253,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -146,12 +320,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -190,150 +364,1621 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AP11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>6</v>
+      </c>
+      <c r="X1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
+        <v>20</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" t="s">
+        <v>20</v>
+      </c>
+      <c r="W2" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U3" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W3" t="s">
+        <v>23</v>
+      </c>
+      <c r="X3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>20</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V4" t="s">
+        <v>20</v>
+      </c>
+      <c r="W4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>19</v>
+      </c>
+      <c r="R5" t="s">
+        <v>20</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" t="s">
+        <v>20</v>
+      </c>
+      <c r="U5" t="s">
+        <v>22</v>
+      </c>
+      <c r="V5" t="s">
+        <v>20</v>
+      </c>
+      <c r="W5" t="s">
+        <v>23</v>
+      </c>
+      <c r="X5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T6" t="s">
+        <v>28</v>
+      </c>
+      <c r="U6" t="s">
+        <v>27</v>
+      </c>
+      <c r="V6" t="s">
+        <v>31</v>
+      </c>
+      <c r="W6" t="s">
+        <v>32</v>
+      </c>
+      <c r="X6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" t="s">
+        <v>20</v>
+      </c>
+      <c r="S7" t="s">
+        <v>24</v>
+      </c>
+      <c r="T7" t="s">
+        <v>20</v>
+      </c>
+      <c r="U7" t="s">
+        <v>25</v>
+      </c>
+      <c r="V7" t="s">
+        <v>20</v>
+      </c>
+      <c r="W7" t="s">
+        <v>26</v>
+      </c>
+      <c r="X7" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>29</v>
+      </c>
+      <c r="R8" t="s">
+        <v>28</v>
+      </c>
+      <c r="S8" t="s">
+        <v>30</v>
+      </c>
+      <c r="T8" t="s">
+        <v>28</v>
+      </c>
+      <c r="U8" t="s">
+        <v>27</v>
+      </c>
+      <c r="V8" t="s">
+        <v>31</v>
+      </c>
+      <c r="W8" t="s">
+        <v>32</v>
+      </c>
+      <c r="X8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>11</v>
+      </c>
+      <c r="O9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>19</v>
+      </c>
+      <c r="R9" t="s">
+        <v>20</v>
+      </c>
+      <c r="S9" t="s">
+        <v>21</v>
+      </c>
+      <c r="T9" t="s">
+        <v>20</v>
+      </c>
+      <c r="U9" t="s">
+        <v>22</v>
+      </c>
+      <c r="V9" t="s">
+        <v>20</v>
+      </c>
+      <c r="W9" t="s">
+        <v>23</v>
+      </c>
+      <c r="X9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" t="s">
+        <v>31</v>
+      </c>
+      <c r="U10" t="s">
+        <v>33</v>
+      </c>
+      <c r="V10" t="s">
+        <v>31</v>
+      </c>
+      <c r="W10" t="s">
+        <v>12</v>
+      </c>
+      <c r="X10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:42" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" t="s">
+        <v>28</v>
+      </c>
+      <c r="S11" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11" t="s">
+        <v>28</v>
+      </c>
+      <c r="U11" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" t="s">
+        <v>31</v>
+      </c>
+      <c r="W11" t="s">
+        <v>32</v>
+      </c>
+      <c r="X11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:AP1 A3:D11 A2:D2 F2:AP2 F3:AP11" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>